--- a/artfynd/A 28480-2026 artfynd.xlsx
+++ b/artfynd/A 28480-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406648</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405950</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406077</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406565</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405863</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405871</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405882</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405891</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405901</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405913</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1831,6 +1886,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405925</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405936</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405945</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405953</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2255,6 +2330,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405957</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,6 +2441,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405959</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405969</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2573,6 +2663,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405971</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2679,6 +2774,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405980</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2785,6 +2885,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405987</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2891,6 +2996,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405995</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2997,6 +3107,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406003</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3103,6 +3218,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406005</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3209,6 +3329,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406041</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3315,6 +3440,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406051</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3421,6 +3551,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406534</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3527,6 +3662,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406541</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3633,6 +3773,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406549</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3739,6 +3884,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406556</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3845,6 +3995,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406579</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3951,6 +4106,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406591</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4057,6 +4217,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406624</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4158,6 +4323,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406634</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4268,6 +4438,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406024</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4378,6 +4553,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406034</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4483,6 +4663,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405824</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4588,6 +4773,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135405847</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4698,6 +4888,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406012</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4803,8 +4998,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135406615</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28480-2026 artfynd.xlsx
+++ b/artfynd/A 28480-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135406648</v>
       </c>
       <c r="B2" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135405950</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135406077</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135406565</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135405863</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>135405871</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135405882</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>135405891</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135405901</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135405913</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>135405925</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>135405936</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>135405945</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135405953</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>135405957</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135405959</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135405969</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135405971</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>135405980</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>135405987</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>135405995</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>135406003</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>135406005</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>135406041</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>135406051</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>135406534</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>135406541</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>135406549</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>135406556</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>135406579</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>135406591</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135406624</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>135406634</v>
       </c>
       <c r="B34" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135406024</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>135406034</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>135405824</v>
       </c>
       <c r="B37" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>135405847</v>
       </c>
       <c r="B38" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>135406012</v>
       </c>
       <c r="B39" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>135406615</v>
       </c>
       <c r="B40" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 28480-2026 artfynd.xlsx
+++ b/artfynd/A 28480-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135406648</v>
       </c>
       <c r="B2" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135405950</v>
       </c>
       <c r="B3" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135406077</v>
       </c>
       <c r="B4" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135406565</v>
       </c>
       <c r="B5" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135405863</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>135405871</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135405882</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>135405891</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135405901</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135405913</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>135405925</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>135405936</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>135405945</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135405953</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>135405957</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135405959</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135405969</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135405971</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>135405980</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>135405987</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>135405995</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>135406003</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>135406005</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>135406041</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>135406051</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>135406534</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>135406541</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>135406549</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>135406556</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>135406579</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>135406591</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135406624</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>135406634</v>
       </c>
       <c r="B34" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 28480-2026 artfynd.xlsx
+++ b/artfynd/A 28480-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135406648</v>
       </c>
       <c r="B2" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135405950</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135406077</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135406565</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28480-2026 artfynd.xlsx
+++ b/artfynd/A 28480-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135406648</v>
       </c>
       <c r="B2" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135405950</v>
       </c>
       <c r="B3" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135406077</v>
       </c>
       <c r="B4" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>135406565</v>
       </c>
       <c r="B5" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>135405863</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>135405871</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>135405882</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>135405891</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>135405901</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135405913</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>135405925</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>135405936</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>135405945</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135405953</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>135405957</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135405959</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135405969</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135405971</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>135405980</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>135405987</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>135405995</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>135406003</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>135406005</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>135406041</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>135406051</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>135406534</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>135406541</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>135406549</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>135406556</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>135406579</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>135406591</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>135406624</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>135406634</v>
       </c>
       <c r="B34" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>135406024</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>135406034</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>135405824</v>
       </c>
       <c r="B37" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>135405847</v>
       </c>
       <c r="B38" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>135406012</v>
       </c>
       <c r="B39" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>135406615</v>
       </c>
       <c r="B40" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
